--- a/sizeok.xlsx
+++ b/sizeok.xlsx
@@ -5,15 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SCRIPTS\pokerchartviewer16\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SCRIPTS\sbch\sbch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D3B64A-DFCC-4917-8217-3A3BD0898FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0428682-F35A-4919-9A7C-7A07FF301748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4830" yWindow="3720" windowWidth="28710" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42180" yWindow="3090" windowWidth="28710" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="100-4bb" sheetId="1" r:id="rId1"/>
+    <sheet name="50-2.5bb" sheetId="2" r:id="rId2"/>
+    <sheet name="50-4bb" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
   <si>
     <t>UTG</t>
   </si>
@@ -456,4 +458,198 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1286FF41-4442-4927-B70A-CFE2F0E01E0D}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424F350C-1C35-4D08-B858-3AC1E85F7DBF}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>